--- a/app/flink-demo-2/src/main/resources/rules/CardLevelRules.xlsx
+++ b/app/flink-demo-2/src/main/resources/rules/CardLevelRules.xlsx
@@ -1,46 +1,134 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ij_proj\flink-demo-parent\app\flink-demo-2\src\main\resources\rules\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{821AF8F3-4257-4D5F-A888-1DAD81ED9DD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="6810" yWindow="3630" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="CardLevelRules" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="28">
+  <si>
+    <t>RuleSet</t>
+  </si>
+  <si>
+    <t>org.example.monthly.rule</t>
+  </si>
+  <si>
+    <t>Import</t>
+  </si>
+  <si>
+    <t>RuleTable CardLevelRules</t>
+  </si>
+  <si>
+    <t>CONDITION</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>ACTION</t>
+  </si>
+  <si>
+    <t>$f : MonthlyConsumptionFact()</t>
+  </si>
+  <si>
+    <t>cardLimit $param</t>
+  </si>
+  <si>
+    <t>monthlyAmount $param</t>
+  </si>
+  <si>
+    <t>$f.setStatus($param);</t>
+  </si>
+  <si>
+    <t>$f.setDescription($param);</t>
+  </si>
+  <si>
+    <t>額度上限區間</t>
+  </si>
+  <si>
+    <t>當月消費金額條件</t>
+  </si>
+  <si>
+    <t>分級狀態</t>
+  </si>
+  <si>
+    <t>分級說明</t>
+  </si>
+  <si>
+    <t>&lt;= 100000</t>
+  </si>
+  <si>
+    <t>"建議提升上限"</t>
+  </si>
+  <si>
+    <t>&gt; 100000 &amp;&amp; &lt;= 500000</t>
+  </si>
+  <si>
+    <t>&gt;= cardLimit - 5000</t>
+  </si>
+  <si>
+    <t>"自動提高上限"</t>
+  </si>
+  <si>
+    <t>&lt; cardLimit - 5000</t>
+  </si>
+  <si>
+    <t>"需促銷"</t>
+  </si>
+  <si>
+    <t>&gt; 500000 &amp;&amp; &lt;= 1000000</t>
+  </si>
+  <si>
+    <t>"可換發黑卡"</t>
+  </si>
+  <si>
+    <t>"不需調整"</t>
+  </si>
+  <si>
+    <t>&gt; 1000000</t>
+  </si>
+  <si>
+    <t>org.example.demo2.model.MonthlyConsumptionFact</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="新細明體"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="新細明體"/>
+      <family val="3"/>
+      <charset val="136"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -64,14 +152,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -396,168 +493,169 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="B1:E15"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
-      <c r="B1" t="str">
-        <v>RuleSet</v>
-      </c>
-      <c r="C1" t="str">
-        <v>org.example.monthly.rule</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="B3" t="str">
-        <v>Import</v>
-      </c>
-      <c r="C3" t="str">
-        <v>org.example.monthly.model.MonthlyConsumptionFact</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="B5" t="str">
-        <v>RuleTable CardLevelRules</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" t="str">
-        <v>CONDITION</v>
-      </c>
-      <c r="C6" t="str">
-        <v/>
-      </c>
-      <c r="D6" t="str">
-        <v>ACTION</v>
-      </c>
-      <c r="E6" t="str">
-        <v>ACTION</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" t="str">
-        <v>$f : MonthlyConsumptionFact()</v>
-      </c>
-      <c r="C7" t="str">
-        <v/>
-      </c>
-      <c r="D7" t="str">
-        <v/>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" t="str">
-        <v>cardLimit $param</v>
-      </c>
-      <c r="C8" t="str">
-        <v>monthlyAmount $param</v>
-      </c>
-      <c r="D8" t="str">
-        <v>$f.setStatus($param);</v>
-      </c>
-      <c r="E8" t="str">
-        <v>$f.setDescription($param);</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" t="str">
-        <v>額度上限區間</v>
-      </c>
-      <c r="C9" t="str">
-        <v>當月消費金額條件</v>
-      </c>
-      <c r="D9" t="str">
-        <v>分級狀態</v>
-      </c>
-      <c r="E9" t="str">
-        <v>分級說明</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" t="str">
-        <v>&lt;= 100000</v>
-      </c>
-      <c r="C10" t="str">
-        <v/>
+    <row r="1" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" t="s">
+        <v>5</v>
       </c>
       <c r="D10">
         <v>1</v>
       </c>
-      <c r="E10" t="str">
-        <v>"建議提升上限"</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" t="str">
-        <v>&gt; 100000 &amp;&amp; &lt;= 500000</v>
-      </c>
-      <c r="C11" t="str">
-        <v>&gt;= cardLimit - 5000</v>
+      <c r="E10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" t="s">
+        <v>19</v>
       </c>
       <c r="D11">
         <v>2</v>
       </c>
-      <c r="E11" t="str">
-        <v>"自動提高上限"</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" t="str">
-        <v>&gt; 100000 &amp;&amp; &lt;= 500000</v>
-      </c>
-      <c r="C12" t="str">
-        <v>&lt; cardLimit - 5000</v>
+      <c r="E11" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" t="s">
+        <v>21</v>
       </c>
       <c r="D12">
         <v>3</v>
       </c>
-      <c r="E12" t="str">
-        <v>"需促銷"</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" t="str">
-        <v>&gt; 500000 &amp;&amp; &lt;= 1000000</v>
-      </c>
-      <c r="C13" t="str">
-        <v>&gt;= cardLimit - 5000</v>
+      <c r="E12" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C13" t="s">
+        <v>19</v>
       </c>
       <c r="D13">
         <v>4</v>
       </c>
-      <c r="E13" t="str">
-        <v>"可換發黑卡"</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" t="str">
-        <v>&gt; 500000 &amp;&amp; &lt;= 1000000</v>
-      </c>
-      <c r="C14" t="str">
-        <v>&lt; cardLimit - 5000</v>
+      <c r="E13" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B14" t="s">
+        <v>23</v>
+      </c>
+      <c r="C14" t="s">
+        <v>21</v>
       </c>
       <c r="D14">
         <v>5</v>
       </c>
-      <c r="E14" t="str">
-        <v>"不需調整"</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" t="str">
-        <v>&gt; 1000000</v>
-      </c>
-      <c r="C15" t="str">
-        <v/>
+      <c r="E14" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B15" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15" t="s">
+        <v>5</v>
       </c>
       <c r="D15">
         <v>5</v>
       </c>
-      <c r="E15" t="str">
-        <v>"不需調整"</v>
+      <c r="E15" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -565,8 +663,11 @@
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B7:C7"/>
   </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E15"/>
+    <ignoredError sqref="A1:E2 A4:E15 A3:B3 E3" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>